--- a/Necessario/Despesa.xlsx
+++ b/Necessario/Despesa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,38 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mensalidades</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>632,42</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Estacio</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Necessario/Despesa.xlsx
+++ b/Necessario/Despesa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Storn\PycharmProjects\App_Financeiro\Necessario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F40C688-209D-4EC2-B480-244059AAAFC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA97247-D255-4779-A209-693DE0E81F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
